--- a/output/test-config/ActivitySoccer.xlsx
+++ b/output/test-config/ActivitySoccer.xlsx
@@ -42363,7 +42363,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>备注</t>
+          <t>设计备注:说明该preset的切片类型、球点/方向、目标点、控球球员和推荐操作；用于策划排查与实例复用</t>
         </is>
       </c>
     </row>
@@ -42391,7 +42391,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>{"x":0,"y":0,"z":58}</t>
+          <t>{"x":0,"y":0,"z":0}</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -42497,6 +42497,11 @@
           <t>["draw_line","slingshot"]</t>
         </is>
       </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>右路单刀；进攻射门基础站位；球点={"x": 12, "y": 0, "z": -23}；方向={"x":0,"y":0,"z":1}；目标={"x": 0, "y": 0, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -42568,6 +42573,11 @@
           <t>["draw_line","slingshot"]</t>
         </is>
       </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>左路单刀；进攻射门基础站位；球点={"x": -12, "y": 0, "z": -23}；方向={"x":0,"y":0,"z":1}；目标={"x": 0, "y": 0, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -42639,6 +42649,11 @@
           <t>["draw_line","slingshot"]</t>
         </is>
       </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>中路突破；进攻射门基础站位；球点={"x": 0, "y": 0, "z": -22}；方向={"x":0,"y":0,"z":1}；目标={"x": 0, "y": 0, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -42710,6 +42725,11 @@
           <t>["draw_line","slingshot"]</t>
         </is>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>中路吊射；进攻射门基础站位；球点={"x": 0, "y": 0, "z": -28}；方向={"x":0,"y":0,"z":1}；目标={"x": 0, "y": 1.5, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -42779,6 +42799,11 @@
       <c r="Q13" t="inlineStr">
         <is>
           <t>["draw_line","slingshot"]</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>中路任意球；任意球+人墙基础站位；球点={"x": 0, "y": 0, "z": -16}；方向={"x":0,"y":0,"z":1}；目标={"x": 0, "y": 1.8, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
         </is>
       </c>
     </row>
@@ -42852,6 +42877,11 @@
           <t>["draw_line","slingshot"]</t>
         </is>
       </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>左侧任意球；任意球+人墙基础站位；球点={"x": -10, "y": 0, "z": -14}；方向={"x":0,"y":0,"z":1}；目标={"x": -2, "y": 1.8, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -42923,6 +42953,11 @@
           <t>["draw_line","slingshot"]</t>
         </is>
       </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>右侧任意球；任意球+人墙基础站位；球点={"x": 10, "y": 0, "z": -14}；方向={"x":0,"y":0,"z":1}；目标={"x": 2, "y": 1.8, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -42994,6 +43029,11 @@
           <t>["draw_line"]</t>
         </is>
       </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>弧线任意球；任意球+人墙基础站位；球点={"x": 4, "y": 0, "z": -18}；方向={"x":0,"y":0,"z":1}；目标={"x": -3, "y": 2.0, "z": 0}；控球home[0]；推荐操作=["draw_line"]</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -43063,6 +43103,11 @@
       <c r="Q17" t="inlineStr">
         <is>
           <t>["draw_line","slingshot"]</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>标准点球；点球基础站位；球点={"x": 0.0, "y": 0.0, "z": -11.0}；方向={"x":0,"y":0,"z":1}；目标={"x": 0, "y": 0.5, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
         </is>
       </c>
     </row>
@@ -43136,6 +43181,11 @@
           <t>["draw_line","slingshot"]</t>
         </is>
       </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>加压点球；点球基础站位；球点={"x": 0.0, "y": 0.0, "z": -11.0}；方向={"x":0,"y":0,"z":1}；目标={"x": 0, "y": 0.5, "z": 0}；控球home[0]；推荐操作=["draw_line","slingshot"]</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -43207,6 +43257,11 @@
           <t>["draw_line"]</t>
         </is>
       </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>左角球；角球传中基础站位；球点={"x": -17.0, "y": 0.0, "z": -1.0}；方向={"x":1,"y":0,"z":1}；目标={"x": 0, "y": 2.0, "z": 0}；控球home[0]；推荐操作=["draw_line"]</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -43278,6 +43333,11 @@
           <t>["draw_line"]</t>
         </is>
       </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>右角球；角球传中基础站位；球点={"x": 17.0, "y": 0.0, "z": -1.0}；方向={"x":-1,"y":0,"z":1}；目标={"x": 0, "y": 2.0, "z": 0}；控球home[0]；推荐操作=["draw_line"]</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -43349,6 +43409,11 @@
           <t>["draw_line"]</t>
         </is>
       </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>后点包抄；角球传中基础站位；球点={"x": 17.0, "y": 0.0, "z": -1.0}；方向={"x":-1,"y":0,"z":1}；目标={"x": -6, "y": 2.0, "z": 0}；控球home[0]；推荐操作=["draw_line"]</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -43384,7 +43449,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": -20, "y": 0, "z": -18.0}, "facing": 45.0}, {"team": "home", "idx": 1, "duty": 3, "pos": {"x": -16.0, "y": 0, "z": -14.0}, "facing": 48.8}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -2}, "facing": 180.0}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": -16.0, "y": 0, "z": -10}, "facing": 180.0}]</t>
+          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": -18.0, "y": 0, "z": -18.0}, "facing": 36.9}, {"team": "home", "idx": 1, "duty": 3, "pos": {"x": -15.0, "y": 0, "z": -14.0}, "facing": 47.0}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -2}, "facing": 180.0}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": -15.0, "y": 0, "z": -10}, "facing": 180.0}]</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -43418,6 +43483,11 @@
       <c r="Q22" t="inlineStr">
         <is>
           <t>["draw_line"]</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>左界外球；界外球二次进攻基础站位；球点={"x": -18, "y": 0, "z": -18}；方向={"x":1,"y":0,"z":0}；目标={"x": -10, "y": 0, "z": -14}；控球home[0]；推荐操作=["draw_line"]</t>
         </is>
       </c>
     </row>
@@ -43455,7 +43525,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": 20, "y": 0, "z": -18.0}, "facing": -45.0}, {"team": "home", "idx": 1, "duty": 3, "pos": {"x": 16.0, "y": 0, "z": -14.0}, "facing": -48.8}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -2}, "facing": 180.0}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": 16.0, "y": 0, "z": -10}, "facing": 180.0}]</t>
+          <t>[{"team": "home", "idx": 0, "duty": 3, "pos": {"x": 18.0, "y": 0, "z": -18.0}, "facing": -36.9}, {"team": "home", "idx": 1, "duty": 3, "pos": {"x": 15.0, "y": 0, "z": -14.0}, "facing": -47.0}, {"team": "away", "idx": 0, "duty": 1, "pos": {"x": 0, "y": 0, "z": -2}, "facing": 180.0}, {"team": "away", "idx": 1, "duty": 2, "pos": {"x": 15.0, "y": 0, "z": -10}, "facing": 180.0}]</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -43489,6 +43559,11 @@
       <c r="Q23" t="inlineStr">
         <is>
           <t>["draw_line"]</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>右界外球；界外球二次进攻基础站位；球点={"x": 18, "y": 0, "z": -18}；方向={"x":-1,"y":0,"z":0}；目标={"x": 10, "y": 0, "z": -14}；控球home[0]；推荐操作=["draw_line"]</t>
         </is>
       </c>
     </row>
@@ -43534,7 +43609,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>{"x":0,"y":0,"z":58}</t>
+          <t>{"x":0,"y":0,"z":0}</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -43560,6 +43635,11 @@
       <c r="Q24" t="inlineStr">
         <is>
           <t>["draw_line"]</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>基础守门；守门扑救基础站位；球点={"x": 0, "y": 0, "z": -18}；方向={"x":0,"y":0,"z":1}；目标=无固定目标点；控球home[0]；推荐操作=["draw_line"]</t>
         </is>
       </c>
     </row>
@@ -43605,7 +43685,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>{"x":0,"y":0,"z":58}</t>
+          <t>{"x":0,"y":0,"z":0}</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -43631,6 +43711,11 @@
       <c r="Q25" t="inlineStr">
         <is>
           <t>["draw_line"]</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>大范围守门；守门扑救基础站位；球点={"x": 0, "y": 0, "z": -18}；方向={"x":0,"y":0,"z":1}；目标=无固定目标点；控球home[0]；推荐操作=["draw_line"]</t>
         </is>
       </c>
     </row>
@@ -43676,7 +43761,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>{"x":0,"y":0,"z":58}</t>
+          <t>{"x":0,"y":0,"z":0}</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -43702,6 +43787,11 @@
       <c r="Q26" t="inlineStr">
         <is>
           <t>["draw_line"]</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>近距扑点；守门扑救基础站位；球点={"x": 0, "y": 0, "z": -11}；方向={"x":0,"y":0,"z":1}；目标=无固定目标点；控球home[0]；推荐操作=["draw_line"]</t>
         </is>
       </c>
     </row>
